--- a/economics/ORC_Group3.xlsx
+++ b/economics/ORC_Group3.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Temperature of the geothermal fluid from the production wells</t>
   </si>
   <si>
-    <t xml:space="preserve">Group3: avg production T at t=100yr (FEFLOW result, see breakthrough curve F3)</t>
+    <t xml:space="preserve">Group3: exact avg production T at t=100yr, extracted directly from FEFLOW post-processing (Stage 12); see ../outputs/Average_Production_Temperature.csv, ../figures/F8_average_production_temperature.png</t>
   </si>
   <si>
     <t xml:space="preserve">Tsource-out</t>
@@ -276,8 +276,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
-    <numFmt numFmtId="166" formatCode="0%"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+    <numFmt numFmtId="166" formatCode="0.00%"/>
+    <numFmt numFmtId="167" formatCode="0%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -396,41 +396,42 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -438,15 +439,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -454,11 +455,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -712,309 +713,309 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="78.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="36.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="78.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="36.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="3" t="n">
+        <v>124.5327</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <f aca="false">B4+12</f>
         <v>26</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <f aca="false">(B2-B3)/LN((273.15+B2)/(273.15+B3))-273.15</f>
-        <v>86.1964947738236</v>
-      </c>
-      <c r="C6" s="0" t="s">
+        <v>85.9782447753919</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <f aca="false">(B5-B4)/LN((273.15+B5)/(273.15+B4))-273.15</f>
         <v>19.9590607511086</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <f aca="false">1-(273.15+B7)/(273.15+B6)</f>
-        <v>0.184327480540489</v>
-      </c>
-      <c r="C8" s="0" t="s">
+        <v>0.18383177871619</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <f aca="false">1-(273.15+B4)/(273.15+B2)</f>
-        <v>0.27878940097953</v>
-      </c>
-      <c r="C9" s="0" t="s">
+        <v>0.277941937127262</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="7" t="n">
         <v>0.52</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="8" t="n">
         <f aca="false">B10*B8</f>
-        <v>0.0958502898810545</v>
-      </c>
-      <c r="D11" s="0" t="s">
+        <v>0.0955925249324185</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="3" t="n">
         <v>4.31</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="3" t="n">
         <v>0.917</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <f aca="false">B14*B13</f>
         <v>137.55</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="8"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <f aca="false">B15*B12*(B2-B3)</f>
-        <v>44463.0375</v>
-      </c>
-      <c r="C16" s="0" t="s">
+        <v>44186.00313435</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="4" t="n">
         <f aca="false">B16*B11</f>
-        <v>4261.7950333672</v>
-      </c>
-      <c r="C17" s="0" t="s">
+        <v>4223.85160628428</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>8000</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="4" t="n">
         <f aca="false">B17*B18/1000</f>
-        <v>34094.3602669376</v>
-      </c>
-      <c r="C19" s="0" t="s">
+        <v>33790.8128502742</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="4" t="n">
         <f aca="false">B17*B20*24/1000</f>
-        <v>3170.77550482519</v>
-      </c>
-      <c r="C21" s="0" t="s">
+        <v>3142.5455950755</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1038,522 +1039,522 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <f aca="false">Base_Case_Group3!B18/8760</f>
         <v>0.91324200913242</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="13" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <f aca="false">C8+12</f>
         <v>17</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <f aca="false">(D8-C8)/LN((273.15+D8)/(273.15+C8))-273.15</f>
         <v>10.9577637616966</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <f aca="false">1-(273.15+E8)/(273.15+Base_Case_Group3!$B$6)</f>
-        <v>0.209376554680137</v>
-      </c>
-      <c r="G8" s="0" t="n">
+        <v>0.208896075719734</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$10*F8</f>
-        <v>0.108875808433671</v>
-      </c>
-      <c r="H8" s="0" t="n">
+        <v>0.108625959374262</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$16*G8</f>
-        <v>4840.94915322914</v>
-      </c>
-      <c r="I8" s="0" t="n">
+        <v>4799.7469813829</v>
+      </c>
+      <c r="I8" s="1" t="n">
         <f aca="false">H8*B8*24/1000*$H$5</f>
-        <v>3289.19284931733</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+        <v>3261.19794899441</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>5.7</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <f aca="false">C9+12</f>
         <v>17.7</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <f aca="false">(D9-C9)/LN((273.15+D9)/(273.15+C9))-273.15</f>
         <v>11.6578675790533</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <f aca="false">1-(273.15+E9)/(273.15+Base_Case_Group3!$B$6)</f>
-        <v>0.207428285175526</v>
-      </c>
-      <c r="G9" s="0" t="n">
+        <v>0.206946622209625</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$10*F9</f>
-        <v>0.107862708291273</v>
-      </c>
-      <c r="H9" s="0" t="n">
+        <v>0.107612243549005</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$16*G9</f>
-        <v>4795.90364360645</v>
-      </c>
-      <c r="I9" s="0" t="n">
+        <v>4754.95493075076</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <f aca="false">H9*B9*24/1000*$H$5</f>
-        <v>2943.23949635026</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+        <v>2918.10932736485</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <f aca="false">C10+12</f>
         <v>21</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <f aca="false">(D10-C10)/LN((273.15+D10)/(273.15+C10))-273.15</f>
         <v>14.9583502073273</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <f aca="false">1-(273.15+E10)/(273.15+Base_Case_Group3!$B$6)</f>
-        <v>0.198243604995603</v>
-      </c>
-      <c r="G10" s="0" t="n">
+        <v>0.19775636030099</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$10*F10</f>
-        <v>0.103086674597713</v>
-      </c>
-      <c r="H10" s="0" t="n">
+        <v>0.102833307356515</v>
+      </c>
+      <c r="H10" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$16*G10</f>
-        <v>4583.54667838843</v>
-      </c>
-      <c r="I10" s="0" t="n">
+        <v>4543.79284117054</v>
+      </c>
+      <c r="I10" s="1" t="n">
         <f aca="false">H10*B10*24/1000*$H$5</f>
-        <v>3114.30020887762</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+        <v>3087.28938249396</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="14" t="n">
         <v>12.5</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <f aca="false">C11+12</f>
         <v>24.5</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <f aca="false">(D11-C11)/LN((273.15+D11)/(273.15+C11))-273.15</f>
         <v>18.4588501469475</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <f aca="false">1-(273.15+E11)/(273.15+Base_Case_Group3!$B$6)</f>
-        <v>0.188502310755837</v>
-      </c>
-      <c r="G11" s="0" t="n">
+        <v>0.188009146066116</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$10*F11</f>
-        <v>0.0980212015930353</v>
-      </c>
-      <c r="H11" s="0" t="n">
+        <v>0.0977647559543802</v>
+      </c>
+      <c r="H11" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$16*G11</f>
-        <v>4358.32036222619</v>
-      </c>
-      <c r="I11" s="0" t="n">
+        <v>4319.83381302921</v>
+      </c>
+      <c r="I11" s="1" t="n">
         <f aca="false">H11*B11*24/1000*$H$5</f>
-        <v>2865.74489571037</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+        <v>2840.43867158085</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="14" t="n">
         <v>16.5</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <f aca="false">C12+12</f>
         <v>28.5</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <f aca="false">(D12-C12)/LN((273.15+D12)/(273.15+C12))-273.15</f>
         <v>22.4594070075169</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <f aca="false">1-(273.15+E12)/(273.15+Base_Case_Group3!$B$6)</f>
-        <v>0.177369443401482</v>
-      </c>
-      <c r="G12" s="0" t="n">
+        <v>0.176869513027585</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$10*F12</f>
-        <v>0.0922321105687707</v>
-      </c>
-      <c r="H12" s="0" t="n">
+        <v>0.0919721467743444</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$16*G12</f>
-        <v>4100.9197909234</v>
-      </c>
-      <c r="I12" s="0" t="n">
+        <v>4063.88156564408</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <f aca="false">H12*B12*24/1000*$H$5</f>
-        <v>2786.37837849042</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+        <v>2761.21268021844</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <f aca="false">C13+12</f>
         <v>33</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <f aca="false">(D13-C13)/LN((273.15+D13)/(273.15+C13))-273.15</f>
         <v>26.9600157288402</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <f aca="false">1-(273.15+E13)/(273.15+Base_Case_Group3!$B$6)</f>
-        <v>0.164845017014198</v>
-      </c>
-      <c r="G13" s="0" t="n">
+        <v>0.164337475275617</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$10*F13</f>
-        <v>0.0857194088473831</v>
-      </c>
-      <c r="H13" s="0" t="n">
+        <v>0.0854554871433209</v>
+      </c>
+      <c r="H13" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$16*G13</f>
-        <v>3811.34529005902</v>
-      </c>
-      <c r="I13" s="0" t="n">
+        <v>3775.93642276218</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <f aca="false">H13*B13*24/1000*$H$5</f>
-        <v>2506.09005373744</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+        <v>2482.80751085733</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="14" t="n">
         <v>23.7</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="1" t="n">
         <f aca="false">C14+12</f>
         <v>35.7</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <f aca="false">(D14-C14)/LN((273.15+D14)/(273.15+C14))-273.15</f>
         <v>29.660372275778</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <f aca="false">1-(273.15+E14)/(273.15+Base_Case_Group3!$B$6)</f>
-        <v>0.157330385353084</v>
-      </c>
-      <c r="G14" s="0" t="n">
+        <v>0.156818276810382</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$10*F14</f>
-        <v>0.0818118003836036</v>
-      </c>
-      <c r="H14" s="0" t="n">
+        <v>0.0815455039413985</v>
+      </c>
+      <c r="H14" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$16*G14</f>
-        <v>3637.60114839868</v>
-      </c>
-      <c r="I14" s="0" t="n">
+        <v>3603.16989274678</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <f aca="false">H14*B14*24/1000*$H$5</f>
-        <v>2471.57557480239</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+        <v>2448.18118740056</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="14" t="n">
         <v>23.7</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <f aca="false">C15+12</f>
         <v>35.7</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <f aca="false">(D15-C15)/LN((273.15+D15)/(273.15+C15))-273.15</f>
         <v>29.660372275778</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <f aca="false">1-(273.15+E15)/(273.15+Base_Case_Group3!$B$6)</f>
-        <v>0.157330385353084</v>
-      </c>
-      <c r="G15" s="0" t="n">
+        <v>0.156818276810382</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$10*F15</f>
-        <v>0.0818118003836036</v>
-      </c>
-      <c r="H15" s="0" t="n">
+        <v>0.0815455039413985</v>
+      </c>
+      <c r="H15" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$16*G15</f>
-        <v>3637.60114839868</v>
-      </c>
-      <c r="I15" s="0" t="n">
+        <v>3603.16989274678</v>
+      </c>
+      <c r="I15" s="1" t="n">
         <f aca="false">H15*B15*24/1000*$H$5</f>
-        <v>2471.57557480239</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+        <v>2448.18118740056</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <v>19.2</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="1" t="n">
         <f aca="false">C16+12</f>
         <v>31.2</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <f aca="false">(D16-C16)/LN((273.15+D16)/(273.15+C16))-273.15</f>
         <v>25.1597744445407</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="1" t="n">
         <f aca="false">1-(273.15+E16)/(273.15+Base_Case_Group3!$B$6)</f>
-        <v>0.169854781435116</v>
-      </c>
-      <c r="G16" s="0" t="n">
+        <v>0.169350284238681</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$10*F16</f>
-        <v>0.0883244863462604</v>
-      </c>
-      <c r="H16" s="0" t="n">
+        <v>0.0880621478041141</v>
+      </c>
+      <c r="H16" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$16*G16</f>
-        <v>3927.17494858201</v>
-      </c>
-      <c r="I16" s="0" t="n">
+        <v>3891.11433889018</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <f aca="false">H16*B16*24/1000*$H$5</f>
-        <v>2582.25202098543</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+        <v>2558.54093516067</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="1" t="n">
         <f aca="false">C17+12</f>
         <v>27</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <f aca="false">(D17-C17)/LN((273.15+D17)/(273.15+C17))-273.15</f>
         <v>20.9591999601927</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <f aca="false">1-(273.15+E17)/(273.15+Base_Case_Group3!$B$6)</f>
-        <v>0.18154426371876</v>
-      </c>
-      <c r="G17" s="0" t="n">
+        <v>0.181046870473426</v>
+      </c>
+      <c r="G17" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$10*F17</f>
-        <v>0.094403017133755</v>
-      </c>
-      <c r="H17" s="0" t="n">
+        <v>0.0941443726461816</v>
+      </c>
+      <c r="H17" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$16*G17</f>
-        <v>4197.44489093129</v>
-      </c>
-      <c r="I17" s="0" t="n">
+        <v>4159.8635448256</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <f aca="false">H17*B17*24/1000*$H$5</f>
-        <v>2851.96255603003</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+        <v>2826.42783319657</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <v>10.2</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="1" t="n">
         <f aca="false">C18+12</f>
         <v>22.2</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="1" t="n">
         <f aca="false">(D18-C18)/LN((273.15+D18)/(273.15+C18))-273.15</f>
         <v>16.1585229781612</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="1" t="n">
         <f aca="false">1-(273.15+E18)/(273.15+Base_Case_Group3!$B$6)</f>
-        <v>0.194903728891929</v>
-      </c>
-      <c r="G18" s="0" t="n">
+        <v>0.194414454482403</v>
+      </c>
+      <c r="G18" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$10*F18</f>
-        <v>0.101349939023803</v>
-      </c>
-      <c r="H18" s="0" t="n">
+        <v>0.10109551633085</v>
+      </c>
+      <c r="H18" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$16*G18</f>
-        <v>4506.32613943808</v>
-      </c>
-      <c r="I18" s="0" t="n">
+        <v>4467.00680146366</v>
+      </c>
+      <c r="I18" s="1" t="n">
         <f aca="false">H18*B18*24/1000*$H$5</f>
-        <v>2963.06376291819</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+        <v>2937.20995164734</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <v>6.1</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19" s="1" t="n">
         <f aca="false">C19+12</f>
         <v>18.1</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="1" t="n">
         <f aca="false">(D19-C19)/LN((273.15+D19)/(273.15+C19))-273.15</f>
         <v>12.0579266744054</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19" s="1" t="n">
         <f aca="false">1-(273.15+E19)/(273.15+Base_Case_Group3!$B$6)</f>
-        <v>0.206314988952603</v>
-      </c>
-      <c r="G19" s="0" t="n">
+        <v>0.205832649412519</v>
+      </c>
+      <c r="G19" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$10*F19</f>
-        <v>0.107283794255354</v>
-      </c>
-      <c r="H19" s="0" t="n">
+        <v>0.10703297769451</v>
+      </c>
+      <c r="H19" s="1" t="n">
         <f aca="false">Base_Case_Group3!$B$16*G19</f>
-        <v>4770.16336711808</v>
-      </c>
-      <c r="I19" s="0" t="n">
+        <v>4729.35948788843</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <f aca="false">H19*B19*24/1000*$H$5</f>
-        <v>3241.09730149393</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
+        <v>3213.37302190775</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I20" s="12" t="n">
         <f aca="false">SUM(I8:I19)</f>
-        <v>34086.4726735158</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
+        <v>33782.9696382233</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15" t="s">
         <v>81</v>
       </c>
     </row>
